--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>중도퇴사일</t>
+          <t>중간정산일</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>예시) 당기 중 중도퇴사 — 당기말 충당부채 대상에서 제외되고 요약표의 '퇴사자 명단'에 표시됨</t>
+          <t>예시) 퇴직금 중간정산 이력 있음 — 재직 상태는 계속 유지되며(퇴사 아님), 재직일수만 입사일(2018-06-01)이 아닌 중간정산일(2023-06-30)부터 다시 기산됨</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액. 인원별 전기 추계액을 다시 계산하지 않고 이 값을 그대로 신뢰함</t>
+          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 앱의 당기말 재계산액과의 증감 비교용 참고값(계산에는 반영되지 않음)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액</t>
+          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 위와 동일</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -922,141 +922,145 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  전기말 잔액과 당기말 회사계상액은 회사가 보고한 값을 그대로 입력받아(신뢰) 재계산액과 대사합니다.</t>
+          <t xml:space="preserve">  감가상각비 앱과 달리 기초(전기말) 잔액을 신뢰하지 않습니다 — 당기말 잔액은 회사계상 입력값과</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  무관하게 재직일수·급여만으로 전액 독립 계산되며, 회사계상 전기말/당기말 잔액은 대사(비교)용으로만 쓰입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>1. 인원 1명 = 1행. '인원정보' 시트에 전기·당기 재직 여부와 무관하게 계속 추가하면 됩니다</t>
-        </is>
-      </c>
+      <c r="A7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (전기에만 있었거나 당기에만 있는 사람도 모두 이 한 시트에 함께 입력 — 앱이 입사일/중도퇴사일로 자동 구분합니다).</t>
+          <t>1. 인원 1명 = 1행. '인원정보' 시트에 전기·당기 재직 여부와 무관하게 계속 추가하면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr"/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (전기에만 있었거나 당기에만 있는 사람도 모두 이 한 시트에 함께 입력 — 앱이 입사일로 자동 구분합니다).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>2. 재직정보</t>
-        </is>
-      </c>
+      <c r="A10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
+          <t>2. 재직정보</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '입사일': 필수. 재직여부·근속일수 판정의 기준이 됩니다.</t>
+          <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '중도퇴사일': 당기 중(또는 그 이전) 퇴사한 인원만 입력. 재직 중이면 비워둡니다.</t>
+          <t xml:space="preserve">   '입사일': 필수. 재직여부·근속일수 판정의 기준이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr"/>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '중간정산일': 퇴직금 중간정산을 받은 이력이 있는 인원만 입력. 중간정산은 재직 상태를 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>3. 임금정보 — '월평균급여(원)'에 결산기준일 현재(또는 최근 급여 수준)의 월 급여를 입력합니다.</t>
+          <t xml:space="preserve">     유지한 채 근속기간만 다시 기산되는 것(퇴사가 아님)이므로, 재직여부 판정에는 영향이 없고</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   앱은 이 값을 연간환산해 1일평균임금 = 월평균급여 × 12 / 365 로 추정한 뒤,</t>
+          <t xml:space="preserve">     재직일수 계산의 기산일이 입사일 대신 이 날짜로 바뀔 뿐입니다. 정산 이력이 없으면 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) 로 인원별 추계액을 계산합니다.</t>
+          <t xml:space="preserve">   ※ 이 템플릿에는 실제 퇴사일 필드가 없습니다 — 진짜 퇴사자까지 추적해야 하면 별도 요청하세요.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 입사일. 당기 결산기준일 이후에 퇴사한 인원은 재직 중으로 간주해 정상 계산됩니다.</t>
-        </is>
-      </c>
+      <c r="A18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr"/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>3. 임금정보 — '월평균급여(원)'에 결산기준일 현재(또는 최근 급여 수준)의 월 급여를 입력합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>4. 전기/당기 인원 자동 판정 (요약표 '인원 변동 명단'에 사용)</t>
+          <t xml:space="preserve">   앱은 이 값을 연간환산해 1일평균임금 = 월평균급여 × 12 / 365 로 추정한 뒤,</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기 재직자 = 입사일 ≤ 전기말 AND (중도퇴사일 없음 OR 중도퇴사일 &gt; 전기말)</t>
+          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) 로 인원별 추계액을 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 재직자 = 입사일 ≤ 당기말 AND (중도퇴사일 없음 OR 중도퇴사일 &gt; 당기말)</t>
+          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   신규입사자 = 당기 재직자 중 전기 재직자가 아니었던 사람 / 퇴사자 = 전기 재직자 중 당기 재직자가 아닌 사람.</t>
-        </is>
-      </c>
+      <c r="A23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr"/>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>4. 전기/당기 인원 자동 판정 (요약표 '인원 변동 명단'에 사용)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+          <t xml:space="preserve">   전기 재직자 = 입사일 ≤ 전기말 / 당기 재직자 = 입사일 ≤ 당기말 (중간정산일은 이 판정에 영향 없음).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기말 값은 '기초잔액'으로 신뢰해 그대로 쓰고, 당기말 값은 앱 재계산액과 비교해 차이(대사)를 표시합니다.</t>
+          <t xml:space="preserve">   신규입사자 = 당기 재직자 중 전기 재직자가 아니었던 사람.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
+          <t xml:space="preserve">   퇴사자 명단은 실제 퇴사일 필드가 없어 항상 비어 있습니다(위 1번 안내 참고).</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1094,36 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -519,7 +520,8 @@
           <t>임금정보</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -572,6 +574,11 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>상여금(연간, 원)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -617,9 +624,12 @@
       <c r="I3" s="5" t="n">
         <v>4200000</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 실제 인원으로 교체(기존 재직자)</t>
+      <c r="J3" s="5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 실제 인원으로 교체(기존 재직자, 연간상여금 600만원 지급)</t>
         </is>
       </c>
     </row>
@@ -663,9 +673,12 @@
       <c r="I4" s="5" t="n">
         <v>3800000</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 기존 재직자</t>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 기존 재직자(상여금 없음)</t>
         </is>
       </c>
     </row>
@@ -709,7 +722,10 @@
       <c r="I5" s="5" t="n">
         <v>3200000</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>예시) 당기 중 신규입사 — 전기 인원명단에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
         </is>
@@ -759,7 +775,10 @@
       <c r="I6" s="5" t="n">
         <v>3500000</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="5" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>예시) 퇴직금 중간정산 이력 있음 — 재직 상태는 계속 유지되며(퇴사 아님), 재직일수만 입사일(2018-06-01)이 아닌 중간정산일(2023-06-30)부터 다시 기산됨</t>
         </is>
@@ -767,9 +786,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="J1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="I1"/>
+    <mergeCell ref="K1"/>
     <mergeCell ref="F1:H1"/>
   </mergeCells>
   <dataValidations count="1">
@@ -889,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1008,122 +1027,143 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>3. 임금정보 — '월평균급여(원)'에 결산기준일 현재(또는 최근 급여 수준)의 월 급여를 입력합니다.</t>
+          <t>3. 임금정보</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   앱은 이 값을 연간환산해 1일평균임금 = 월평균급여 × 12 / 365 로 추정한 뒤,</t>
+          <t xml:space="preserve">   '월평균급여(원)': 결산기준일 현재(또는 최근 급여 수준)의 월 급여(기본급 등, 상여금 제외).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) 로 인원별 추계액을 계산합니다.</t>
+          <t xml:space="preserve">   '상여금(연간, 원)': 연간 지급된 상여금 총액. 상여금이 없으면 0 또는 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
+          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr"/>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   앱은 이 급여기준액을 연간환산해 1일평균임금 = 급여기준액 × 12 / 365 로 추정한 뒤,</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>4. 전기/당기 인원 자동 판정 (요약표 '인원 변동 명단'에 사용)</t>
+          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) 로 인원별 추계액을 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기 재직자 = 입사일 ≤ 전기말 / 당기 재직자 = 입사일 ≤ 당기말 (중간정산일은 이 판정에 영향 없음).</t>
+          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   신규입사자 = 당기 재직자 중 전기 재직자가 아니었던 사람.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 명단은 실제 퇴사일 필드가 없어 항상 비어 있습니다(위 1번 안내 참고).</t>
+          <t>4. 전기/당기 인원 자동 판정 (요약표 '인원 변동 명단'에 사용)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr"/>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   전기 재직자 = 입사일 ≤ 전기말 / 당기 재직자 = 입사일 ≤ 당기말 (중간정산일은 이 판정에 영향 없음).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+          <t xml:space="preserve">   신규입사자 = 당기 재직자 중 전기 재직자가 아니었던 사람.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   퇴사자 명단은 실제 퇴사일 필드가 없어 항상 비어 있습니다(위 1번 안내 참고).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
-        </is>
-      </c>
+      <c r="A31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
-        </is>
-      </c>
+      <c r="A35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr"/>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -94,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -482,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -495,7 +497,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -521,7 +524,8 @@
         </is>
       </c>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -579,6 +583,11 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>배수(임원)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -627,7 +636,8 @@
       <c r="J3" s="5" t="n">
         <v>6000000</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 실제 인원으로 교체(기존 재직자, 연간상여금 600만원 지급)</t>
         </is>
@@ -676,7 +686,8 @@
       <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 기존 재직자(상여금 없음)</t>
         </is>
@@ -725,7 +736,8 @@
       <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>예시) 당기 중 신규입사 — 전기 인원명단에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
         </is>
@@ -778,18 +790,71 @@
       <c r="J6" s="5" t="n">
         <v>4200000</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>예시) 퇴직금 중간정산 이력 있음 — 재직 상태는 계속 유지되며(퇴사 아님), 재직일수만 입사일(2018-06-01)이 아닌 중간정산일(2023-06-30)부터 다시 기산됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>임원</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>EMP-2001</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>예시)정대표</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>예시) 임원퇴직금지급규정상 배수 2배 적용 — 부서명이 정확히 '임원'인 인원에만 배수가 적용됨</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="L1"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="K1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F3:F300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="제조원가 또는 판관비 중 선택하세요." type="list">
@@ -815,7 +880,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>퇴직급여충당부채 기준정보 (회사계상액 — 대사용)</t>
         </is>
@@ -844,8 +909,8 @@
           <t>전기말 회사계상 퇴직급여충당부채(제조원가분)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 앱의 당기말 재계산액과의 증감 비교용 참고값(계산에는 반영되지 않음)</t>
         </is>
@@ -857,8 +922,8 @@
           <t>전기말 회사계상 퇴직급여충당부채(판관비분)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 위와 동일</t>
         </is>
@@ -870,8 +935,8 @@
           <t>당기말 회사계상 퇴직급여충당부채(제조원가분)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>당기말 재무제표상 회사 계상액 — 앱의 인원별 재계산 합계와 비교해 차이(대사)를 표시함</t>
         </is>
@@ -883,15 +948,15 @@
           <t>당기말 회사계상 퇴직급여충당부채(판관비분)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>당기말 재무제표상 회사 계상액</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>※ 결산기준일(당기말/전기말)은 이 시트에 입력하지 않습니다 — 실행 시 파일명(fy&lt;연도&gt;)과 --fiscal-month 옵션으로 자동 결정됩니다.</t>
         </is>
@@ -908,262 +973,283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>퇴직급여충당부채 검증앱(일반기업회계기준·퇴직금 추계액 방식) — 입력 템플릿 작성 안내</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr"/>
+      <c r="A2" s="12" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>핵심 원칙: 결산기준일 현재 재직 중인 임직원을 대상으로, 근로기준법상 퇴직금 산정 방식(간편식)으로</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  개인별 퇴직금 추계액을 계산해 합산한 값을 '재계산된 퇴직급여충당부채'로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  감가상각비 앱과 달리 기초(전기말) 잔액을 신뢰하지 않습니다 — 당기말 잔액은 회사계상 입력값과</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  무관하게 재직일수·급여만으로 전액 독립 계산되며, 회사계상 전기말/당기말 잔액은 대사(비교)용으로만 쓰입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr"/>
+      <c r="A7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>1. 인원 1명 = 1행. '인원정보' 시트에 전기·당기 재직 여부와 무관하게 계속 추가하면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   (전기에만 있었거나 당기에만 있는 사람도 모두 이 한 시트에 함께 입력 — 앱이 입사일로 자동 구분합니다).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>2. 재직정보</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   '입사일': 필수. 재직여부·근속일수 판정의 기준이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   '중간정산일': 퇴직금 중간정산을 받은 이력이 있는 인원만 입력. 중간정산은 재직 상태를 그대로</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">     유지한 채 근속기간만 다시 기산되는 것(퇴사가 아님)이므로, 재직여부 판정에는 영향이 없고</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">     재직일수 계산의 기산일이 입사일 대신 이 날짜로 바뀔 뿐입니다. 정산 이력이 없으면 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   ※ 이 템플릿에는 실제 퇴사일 필드가 없습니다 — 진짜 퇴사자까지 추적해야 하면 별도 요청하세요.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>3. 임금정보</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   '월평균급여(원)': 결산기준일 현재(또는 최근 급여 수준)의 월 급여(기본급 등, 상여금 제외).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   '상여금(연간, 원)': 연간 지급된 상여금 총액. 상여금이 없으면 0 또는 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   앱은 이 급여기준액을 연간환산해 1일평균임금 = 급여기준액 × 12 / 365 로 추정한 뒤,</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) 로 인원별 추계액을 계산합니다.</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) × 배수 로 인원별 추계액을 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr"/>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 1배로 계산됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>4. 전기/당기 인원 자동 판정 (요약표 '인원 변동 명단'에 사용)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   전기 재직자 = 입사일 ≤ 전기말 / 당기 재직자 = 입사일 ≤ 당기말 (중간정산일은 이 판정에 영향 없음).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   신규입사자 = 당기 재직자 중 전기 재직자가 아니었던 사람.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   퇴사자 명단은 실제 퇴사일 필드가 없어 항상 비어 있습니다(위 1번 안내 참고).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="인원정보" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="기준정보" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="작성안내" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="당기인원정보" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="전기인원정보" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="기준정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="작성안내" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -739,7 +740,7 @@
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>예시) 당기 중 신규입사 — 전기 인원명단에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
+          <t>예시) 당기 중 신규입사 — '전기인원정보'에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
         </is>
       </c>
     </row>
@@ -871,6 +872,393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>인적사항</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>재직정보</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>임금정보</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>사업장</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>직급</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>원가구분(제조원가/판관비)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>입사일</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>중간정산일</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>월평균급여(원)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>상여금(연간, 원)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>배수(임원)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>생산1팀</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1001</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>예시)홍길동</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>제조원가</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 당기와 동일 인원(전기 시점 급여). 이 시트의 급여는 계산에 쓰이지 않음(매칭용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>경영지원팀</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1002</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>예시)김영희</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="5" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 당기와 동일 인원</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>제2공장</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>생산2팀</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1004</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>예시)박민수</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>사원</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>제조원가</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 당기와 동일 인원(중간정산 이력 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>임원</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>EMP-2001</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>예시)정대표</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 당기와 동일 인원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>생산1팀</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>EMP-0999</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>예시)최과장</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>제조원가</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2012-02-01</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="5" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>예시) 당기 중 퇴사 — '당기인원정보'에는 이 사번이 없어 요약표의 '퇴사자 명단'에 자동 표시됨</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="L1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F3:F300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="제조원가 또는 판관비 중 선택하세요." type="list">
+      <formula1>"제조원가,판관비"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -967,13 +1355,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1023,235 +1411,273 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1. 인원 1명 = 1행. '인원정보' 시트에 전기·당기 재직 여부와 무관하게 계속 추가하면 됩니다</t>
+          <t>0. 시트 구성 — '당기인원정보'와 '전기인원정보' 두 시트로 나뉩니다(회사별 파일을 따로 만들 필요 없음).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (전기에만 있었거나 당기에만 있는 사람도 모두 이 한 시트에 함께 입력 — 앱이 입사일로 자동 구분합니다).</t>
+          <t xml:space="preserve">   '당기인원정보': 이번 결산기준일 현재 재직 중인 인원 전체. 퇴직금 추계액 계산에 실제로 쓰이는 시트입니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '전기인원정보': 직전 결산기준일 현재 재직 중이었던 인원 전체(회사가 작년에 준 인원현황을 그대로 붙여넣으면 됨).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2. 재직정보</t>
+          <t xml:space="preserve">     이 시트는 급여 등 금액 정보를 계산에 쓰지 않고, 사번(없으면 성명) 기준으로 '당기인원정보'와 매칭해</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
+          <t xml:space="preserve">     신규입사자/퇴사자 명단을 만드는 데에만 사용됩니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '입사일': 필수. 재직여부·근속일수 판정의 기준이 됩니다.</t>
+          <t xml:space="preserve">   ※ 사번이 두 시트에서 반드시 동일해야 정확히 매칭됩니다. 사번이 없으면 성명으로 매칭하니 동명이인에 주의하세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   '중간정산일': 퇴직금 중간정산을 받은 이력이 있는 인원만 입력. 중간정산은 재직 상태를 그대로</t>
-        </is>
-      </c>
+      <c r="A14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     유지한 채 근속기간만 다시 기산되는 것(퇴사가 아님)이므로, 재직여부 판정에는 영향이 없고</t>
+          <t>1. 인원 1명 = 1행. 두 시트 모두 같은 컬럼 구조입니다. 계속 재직 중인 사람은 두 시트 모두에,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     재직일수 계산의 기산일이 입사일 대신 이 날짜로 바뀔 뿐입니다. 정산 이력이 없으면 비워둡니다.</t>
+          <t xml:space="preserve">   당기 신규입사자는 '당기인원정보'에만, 당기 중 퇴사한 사람은 '전기인원정보'에만 입력하면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 이 템플릿에는 실제 퇴사일 필드가 없습니다 — 진짜 퇴사자까지 추적해야 하면 별도 요청하세요.</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>2. 재직정보</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>3. 임금정보</t>
+          <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '월평균급여(원)': 결산기준일 현재(또는 최근 급여 수준)의 월 급여(기본급 등, 상여금 제외).</t>
+          <t xml:space="preserve">   '입사일': 필수. 근속일수 계산의 기준이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '상여금(연간, 원)': 연간 지급된 상여금 총액. 상여금이 없으면 0 또는 비워둡니다.</t>
+          <t xml:space="preserve">   '중간정산일': 퇴직금 중간정산을 받은 이력이 있는 인원만 입력. 중간정산은 재직 상태를 그대로</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
+          <t xml:space="preserve">     유지한 채 근속기간만 다시 기산되는 것(퇴사가 아님)이므로, 재직일수 계산의 기산일이</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   앱은 이 급여기준액을 연간환산해 1일평균임금 = 급여기준액 × 12 / 365 로 추정한 뒤,</t>
+          <t xml:space="preserve">     입사일 대신 이 날짜로 바뀔 뿐입니다. 정산 이력이 없으면 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) × 배수 로 인원별 추계액을 계산합니다.</t>
-        </is>
-      </c>
+      <c r="A24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
+          <t>3. 임금정보 ('당기인원정보' 시트에서만 실제 계산에 쓰임)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+          <t xml:space="preserve">   '월평균급여(원)': 결산기준일 현재(또는 최근 급여 수준)의 월 급여(기본급 등, 상여금 제외).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 1배로 계산됨).</t>
+          <t xml:space="preserve">   '상여금(연간, 원)': 연간 지급된 상여금 총액. 상여금이 없으면 0 또는 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
+          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   앱은 이 급여기준액을 연간환산해 1일평균임금 = 급여기준액 × 12 / 365 로 추정한 뒤,</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>4. 전기/당기 인원 자동 판정 (요약표 '인원 변동 명단'에 사용)</t>
+          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) × 배수 로 인원별 추계액을 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전기 재직자 = 입사일 ≤ 전기말 / 당기 재직자 = 입사일 ≤ 당기말 (중간정산일은 이 판정에 영향 없음).</t>
+          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = 당기 재직자 중 전기 재직자가 아니었던 사람.</t>
+          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 명단은 실제 퇴사일 필드가 없어 항상 비어 있습니다(위 1번 안내 참고).</t>
+          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 1배로 계산됨).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr"/>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
-        </is>
-      </c>
+      <c r="A35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
+          <t xml:space="preserve">   신규입사자 = '당기인원정보'에는 있으나 '전기인원정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr"/>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   퇴사자 = '전기인원정보'에는 있으나 '당기인원정보'에는 없는 사번(또는 성명).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   '전기인원정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
-        </is>
-      </c>
+      <c r="A40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr"/>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
           <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx</t>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>
       </c>
     </row>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="당기인원정보" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="전기인원정보" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="당기정보" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="전기정보" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="기준정보" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="작성안내" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -740,7 +740,7 @@
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>예시) 당기 중 신규입사 — '전기인원정보'에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
+          <t>예시) 당기 중 신규입사 — '전기정보'에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>예시) 당기 중 퇴사 — '당기인원정보'에는 이 사번이 없어 요약표의 '퇴사자 명단'에 자동 표시됨</t>
+          <t>예시) 당기 중 퇴사 — '당기정보'에는 이 사번이 없어 요약표의 '퇴사자 명단'에 자동 표시됨</t>
         </is>
       </c>
     </row>
@@ -1411,28 +1411,28 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>0. 시트 구성 — '당기인원정보'와 '전기인원정보' 두 시트로 나뉩니다(회사별 파일을 따로 만들 필요 없음).</t>
+          <t>0. 시트 구성 — '당기정보'와 '전기정보' 두 시트로 나뉩니다(회사별 파일을 따로 만들 필요 없음).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기인원정보': 이번 결산기준일 현재 재직 중인 인원 전체. 퇴직금 추계액 계산에 실제로 쓰이는 시트입니다.</t>
+          <t xml:space="preserve">   '당기정보': 이번 결산기준일 현재 재직 중인 인원 전체. 퇴직금 추계액 계산에 실제로 쓰이는 시트입니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기인원정보': 직전 결산기준일 현재 재직 중이었던 인원 전체(회사가 작년에 준 인원현황을 그대로 붙여넣으면 됨).</t>
+          <t xml:space="preserve">   '전기정보': 직전 결산기준일 현재 재직 중이었던 인원 전체(회사가 작년에 준 인원현황을 그대로 붙여넣으면 됨).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이 시트는 급여 등 금액 정보를 계산에 쓰지 않고, 사번(없으면 성명) 기준으로 '당기인원정보'와 매칭해</t>
+          <t xml:space="preserve">     이 시트는 급여 등 금액 정보를 계산에 쓰지 않고, 사번(없으면 성명) 기준으로 '당기정보'와 매칭해</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 신규입사자는 '당기인원정보'에만, 당기 중 퇴사한 사람은 '전기인원정보'에만 입력하면 됩니다.</t>
+          <t xml:space="preserve">   당기 신규입사자는 '당기정보'에만, 당기 중 퇴사한 사람은 '전기정보'에만 입력하면 됩니다.</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>3. 임금정보 ('당기인원정보' 시트에서만 실제 계산에 쓰임)</t>
+          <t>3. 임금정보 ('당기정보' 시트에서만 실제 계산에 쓰임)</t>
         </is>
       </c>
     </row>
@@ -1598,21 +1598,21 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기인원정보'에는 있으나 '전기인원정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 = '전기인원정보'에는 있으나 '당기인원정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기인원정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1544,138 +1544,179 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   앱은 이 급여기준액을 연간환산해 1일평균임금 = 급여기준액 × 12 / 365 로 추정한 뒤,</t>
-        </is>
-      </c>
+      <c r="A29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365) × 배수 로 인원별 추계액을 계산합니다.</t>
+          <t xml:space="preserve">   [일반 직원] 근로기준법 간편 산식</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일).</t>
+          <t xml:space="preserve">     1일평균임금 = 급여기준액 × 12 / 365</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+          <t xml:space="preserve">     재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 1배로 계산됨).</t>
+          <t xml:space="preserve">     퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
-        </is>
-      </c>
+      <c r="A34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr"/>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   [임원] '부서' 값이 정확히 '임원'인 행 — 소득세법상 임원 퇴직금 한도 산식으로 계산됩니다(위 일반 직원 산식과 다름).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
+          <t xml:space="preserve">     근속연수 = 당기 결산기준일의 연도 − 기산일의 연도</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 13 − 기산일의 월</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">     퇴직금 추계액 = (급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) × 배수</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr"/>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
-        </is>
-      </c>
+      <c r="A42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr"/>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
-        </is>
-      </c>
+      <c r="A47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr"/>
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1300,7 +1300,7 @@
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 앱의 당기말 재계산액과의 증감 비교용 참고값(계산에는 반영되지 않음)</t>
+          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 앱이 '전기정보' 시트로 인별 재계산한 전기말 잔액과 비교해 차이(대사)를 표시함(재계산 자체에는 반영되지 않음)</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1394,14 +1394,14 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  감가상각비 앱과 달리 기초(전기말) 잔액을 신뢰하지 않습니다 — 당기말 잔액은 회사계상 입력값과</t>
+          <t xml:space="preserve">  감가상각비 앱과 달리 기초(전기말) 잔액도 회사계상 입력값을 신뢰하지 않고, 전기말 잔액 역시</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  무관하게 재직일수·급여만으로 전액 독립 계산되며, 회사계상 전기말/당기말 잔액은 대사(비교)용으로만 쓰입니다.</t>
+          <t xml:space="preserve">  인원별로 동일한 방식으로 독립 재계산합니다 — 회사계상 전기말/당기말 잔액은 대사(비교)용으로만 쓰입니다.</t>
         </is>
       </c>
     </row>
@@ -1418,28 +1418,28 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기정보': 이번 결산기준일 현재 재직 중인 인원 전체. 퇴직금 추계액 계산에 실제로 쓰이는 시트입니다.</t>
+          <t xml:space="preserve">   '당기정보': 이번 결산기준일 현재 재직 중인 인원 전체 + 급여정보. 당기말 추계액 계산에 쓰입니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보': 직전 결산기준일 현재 재직 중이었던 인원 전체(회사가 작년에 준 인원현황을 그대로 붙여넣으면 됨).</t>
+          <t xml:space="preserve">   '전기정보': 직전 결산기준일 현재 재직 중이었던 인원 전체 + 그 시점 급여정보(회사가 작년에 준</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이 시트는 급여 등 금액 정보를 계산에 쓰지 않고, 사번(없으면 성명) 기준으로 '당기정보'와 매칭해</t>
+          <t xml:space="preserve">     인원현황을 그대로 붙여넣으면 됨). 이 시트도 같은 산식으로 전기말 추계액을 계산하는 데 쓰이고,</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     신규입사자/퇴사자 명단을 만드는 데에만 사용됩니다.</t>
+          <t xml:space="preserve">     사번(없으면 성명) 기준으로 '당기정보'와 매칭해 신규입사자/퇴사자 명단을 만드는 데에도 쓰입니다.</t>
         </is>
       </c>
     </row>
@@ -1451,19 +1451,23 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ '당기 퇴직급여(전입액에 해당)' = 인원별 (당기말 추계액 − 전기말 추계액)의 합계로 요약표에 자동 산출됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>1. 인원 1명 = 1행. 두 시트 모두 같은 컬럼 구조입니다. 계속 재직 중인 사람은 두 시트 모두에,</t>
+          <t xml:space="preserve">     신규입사자는 전기말 추계액을 0으로 보고, 퇴사자는 '당기 퇴직급여' 계산에 포함되지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 신규입사자는 '당기정보'에만, 당기 중 퇴사한 사람은 '전기정보'에만 입력하면 됩니다.</t>
+          <t xml:space="preserve">     (당기말 표에 아예 나타나지 않는 인원이므로 — 이 부분은 별도 지급액 관리가 필요합니다).</t>
         </is>
       </c>
     </row>
@@ -1473,250 +1477,267 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>2. 재직정보</t>
+          <t>1. 인원 1명 = 1행. 두 시트 모두 같은 컬럼 구조입니다. 계속 재직 중인 사람은 두 시트 모두에,</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
+          <t xml:space="preserve">   당기 신규입사자는 '당기정보'에만, 당기 중 퇴사한 사람은 '전기정보'에만 입력하면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   '입사일': 필수. 근속일수 계산의 기준이 됩니다.</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '중간정산일': 퇴직금 중간정산을 받은 이력이 있는 인원만 입력. 중간정산은 재직 상태를 그대로</t>
+          <t>2. 재직정보</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     유지한 채 근속기간만 다시 기산되는 것(퇴사가 아님)이므로, 재직일수 계산의 기산일이</t>
+          <t xml:space="preserve">   '원가구분': 급여를 제조원가(생산직 등)로 처리하는지 판관비(관리직 등)로 처리하는지 선택.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     입사일 대신 이 날짜로 바뀔 뿐입니다. 정산 이력이 없으면 비워둡니다.</t>
+          <t xml:space="preserve">   '입사일': 필수. 근속일수 계산의 기준이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '중간정산일': 퇴직금 중간정산을 받은 이력이 있는 인원만 입력. 중간정산은 재직 상태를 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>3. 임금정보 ('당기정보' 시트에서만 실제 계산에 쓰임)</t>
+          <t xml:space="preserve">     유지한 채 근속기간만 다시 기산되는 것(퇴사가 아님)이므로, 재직일수 계산의 기산일이</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '월평균급여(원)': 결산기준일 현재(또는 최근 급여 수준)의 월 급여(기본급 등, 상여금 제외).</t>
+          <t xml:space="preserve">     입사일 대신 이 날짜로 바뀔 뿐입니다. 정산 이력이 없으면 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   '상여금(연간, 원)': 연간 지급된 상여금 총액. 상여금이 없으면 0 또는 비워둡니다.</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
+          <t>3. 임금정보 (두 시트 모두 동일 산식 — '당기정보'는 당기말, '전기정보'는 전기말 추계액에 각각 쓰임)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '월평균급여(원)': 결산기준일 현재(또는 최근 급여 수준)의 월 급여(기본급 등, 상여금 제외).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [일반 직원] 근로기준법 간편 산식</t>
+          <t xml:space="preserve">   '상여금(연간, 원)': 연간 지급된 상여금 총액. 상여금이 없으면 0 또는 비워둡니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1일평균임금 = 급여기준액 × 12 / 365</t>
+          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일)</t>
-        </is>
-      </c>
+      <c r="A32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365)</t>
+          <t xml:space="preserve">   [일반 직원] 근로기준법 간편 산식</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr"/>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     1일평균임금 = 급여기준액 × 12 / 365</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [임원] '부서' 값이 정확히 '임원'인 행 — 소득세법상 임원 퇴직금 한도 산식으로 계산됩니다(위 일반 직원 산식과 다름).</t>
+          <t xml:space="preserve">     재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     근속연수 = 당기 결산기준일의 연도 − 기산일의 연도</t>
+          <t xml:space="preserve">     퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 13 − 기산일의 월</t>
-        </is>
-      </c>
+      <c r="A37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     퇴직금 추계액 = (급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) × 배수</t>
+          <t xml:space="preserve">   [임원] '부서' 값이 정확히 '임원'인 행 — 소득세법상 임원 퇴직금 한도 산식으로 계산됩니다(위 일반 직원 산식과 다름).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+          <t xml:space="preserve">     근속연수 = 당기 결산기준일의 연도 − 기산일의 연도</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
+          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 13 − 기산일의 월</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
+          <t xml:space="preserve">     퇴직금 추계액 = (급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) × 배수</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr"/>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
+          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
-        </is>
-      </c>
+      <c r="A45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr"/>
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   두 값 모두 앱 재계산액과의 대사(비교)용 참고값일 뿐, 계산 자체에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
-        </is>
-      </c>
+      <c r="A50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr"/>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   네 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   반영되지 않습니다. 모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
-        </is>
-      </c>
+      <c r="A54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr"/>
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="당기정보" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="전기정보" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="기준정보" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="작성안내" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="당기퇴사자" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="기준정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="작성안내" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1259,98 +1260,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>퇴직급여충당부채 기준정보 (회사계상액 — 대사용)</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>퇴사자 지급정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>실제지급액(원)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>금액(원)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>전기말 회사계상 퇴직급여충당부채(제조원가분)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 앱이 '전기정보' 시트로 인별 재계산한 전기말 잔액과 비교해 차이(대사)를 표시함(재계산 자체에는 반영되지 않음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>전기말 회사계상 퇴직급여충당부채(판관비분)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 위와 동일</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>당기말 회사계상 퇴직급여충당부채(제조원가분)</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>당기말 재무제표상 회사 계상액 — 앱의 인원별 재계산 합계와 비교해 차이(대사)를 표시함</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>당기말 회사계상 퇴직급여충당부채(판관비분)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>당기말 재무제표상 회사 계상액</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>※ 결산기준일(당기말/전기말)은 이 시트에 입력하지 않습니다 — 실행 시 파일명(fy&lt;연도&gt;)과 --fiscal-month 옵션으로 자동 결정됩니다.</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EMP-0999</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>예시)최과장</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>38500000</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>예시) 전기정보에 있는 사번으로 매칭 — 전기말 추계액과 자동 대사됨. 사번 없으면 성명으로 매칭.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1361,7 +1332,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>퇴직급여충당부채 기준정보 (회사계상액 — 대사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>전기말 회사계상 퇴직급여충당부채(제조원가분)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 앱이 '전기정보' 시트로 인별 재계산한 전기말 잔액과 비교해 차이(대사)를 표시함(재계산 자체에는 반영되지 않음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>전기말 회사계상 퇴직급여충당부채(판관비분)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전기말 재무제표(또는 결산정산표)상 실제 계상액 — 위와 동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>당기말 회사계상 퇴직급여충당부채(제조원가분)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>당기말 재무제표상 회사 계상액 — 앱의 인원별 재계산 합계와 비교해 차이(대사)를 표시함</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>당기말 회사계상 퇴직급여충당부채(판관비분)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>당기말 재무제표상 회사 계상액</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>당기 퇴직급여충당부채 차변(당기지급액, 분개장 기준)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>분개장분석(journal_analyzer)에서 '퇴직급여충당부채' 계정의 당기 차변(퇴직금 지급으로 인한 감소) 합계를 뽑아 입력. 전기말(회사계상)+당기 퇴직급여(재계산)-이 값이 당기말(회사계상)과 맞는지 요약표에서 자동 검증(T계정 tie-out). 모르면 비워둬도 됨(해당 검증만 생략).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>※ 결산기준일(당기말/전기말)은 이 시트에 입력하지 않습니다 — 실행 시 파일명(fy&lt;연도&gt;)과 --fiscal-month 옵션으로 자동 결정됩니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1684,60 +1770,119 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>5. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸만 입력합니다.</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   네 값 모두 인별 재계산액과의 대사(비교)용 참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반영되지 않습니다. 모르면 비워둬도 앱 실행에는 문제 없습니다(해당 대사만 생략됨).</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr"/>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>6. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
-        </is>
-      </c>
+      <c r="A56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr"/>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>7. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1765,124 +1765,166 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr"/>
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   퇴사자 명단의 '비고'에는 다음 두 가지가 자동으로 표시됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
+          <t xml:space="preserve">     - 전기 결산기준일 기준 근속기간이 1년 미만이면 '전기 퇴직급여설정대상 아님(근속기간 1년 미만으로 추정)'</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+          <t xml:space="preserve">       (근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건을 충족하지 못하므로, 이 인원은 애초에 전기말</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
+          <t xml:space="preserve">       퇴직급여충당부채 설정 대상이 아니었을 가능성이 있다는 안내입니다).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+          <t xml:space="preserve">     - '당기퇴사자' 시트(아래 5번)에 대응하는 지급액 입력이 없으면 '명단 비교 시 차이 있음' 경고.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
-        </is>
-      </c>
+      <c r="A55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr"/>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
-        </is>
-      </c>
+      <c r="A62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr"/>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr"/>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
           <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1708,223 +1708,230 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     퇴직금 추계액 = (급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) × 배수</t>
+          <t xml:space="preserve">     퇴직금 추계액 = [(급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) / 10] × 배수</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+          <t xml:space="preserve">     (평균급여 × 10% × 근속연수 × 배수 구조 — '10%'는 근속월 나머지항이 아니라 전체에 걸리는 계수입니다)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
+          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr"/>
-    </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
-        </is>
-      </c>
+      <c r="A46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 명단의 '비고'에는 다음 두 가지가 자동으로 표시됩니다.</t>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 전기 결산기준일 기준 근속기간이 1년 미만이면 '전기 퇴직급여설정대상 아님(근속기간 1년 미만으로 추정)'</t>
+          <t xml:space="preserve">   퇴사자 명단의 '비고'에는 다음 두 가지가 자동으로 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       (근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건을 충족하지 못하므로, 이 인원은 애초에 전기말</t>
+          <t xml:space="preserve">     - 전기 결산기준일 기준 근속기간이 1년 미만이면 '전기 퇴직급여설정대상 아님(근속기간 1년 미만으로 추정)'</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       퇴직급여충당부채 설정 대상이 아니었을 가능성이 있다는 안내입니다).</t>
+          <t xml:space="preserve">       (근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건을 충족하지 못하므로, 이 인원은 애초에 전기말</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">       퇴직급여충당부채 설정 대상이 아니었을 가능성이 있다는 안내입니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">     - '당기퇴사자' 시트(아래 5번)에 대응하는 지급액 입력이 없으면 '명단 비교 시 차이 있음' 경고.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr"/>
-    </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
-        </is>
-      </c>
+      <c r="A56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr"/>
-    </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
-        </is>
-      </c>
+      <c r="A63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr"/>
-    </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
-        </is>
-      </c>
+      <c r="A70" s="12" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr"/>
-    </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
-        </is>
-      </c>
+      <c r="A74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1646,7 +1646,7 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (상여금 중 최근 3개월분 상당액만 가산)</t>
+          <t xml:space="preserve">   급여기준액 = 월평균급여 + 상여금(연간) × 3 / 12  (임원 산식·화면 표시용. 상여금 최근 3개월분 상당액 가산)</t>
         </is>
       </c>
     </row>
@@ -1656,282 +1656,289 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [일반 직원] 근로기준법 간편 산식</t>
+          <t xml:space="preserve">   [일반 직원] 근로기준법 평균임금 산식</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1일평균임금 = 급여기준액 × 12 / 365</t>
+          <t xml:space="preserve">     1일평균임금 = (월평균급여 × 3 + 상여금(연간) / 4) / 92</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일)</t>
+          <t xml:space="preserve">       (최근 3개월간 임금총액 ÷ 최근 3개월간 총일수(92일 근사) — 근로기준법상 평균임금 정의 그대로)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">     재직일수 = 당기 결산기준일 − 기산일(중간정산일이 있으면 그 날짜, 없으면 입사일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">     퇴직금 추계액 = 1일평균임금 × 30일 × (재직일수 / 365)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   [임원] '부서' 값이 정확히 '임원'인 행 — 소득세법상 임원 퇴직금 한도 산식으로 계산됩니다(위 일반 직원 산식과 다름).</t>
-        </is>
-      </c>
+      <c r="A38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     근속연수 = 당기 결산기준일의 연도 − 기산일의 연도</t>
+          <t xml:space="preserve">   [임원] '부서' 값이 정확히 '임원'인 행 — 소득세법상 임원 퇴직금 한도 산식으로 계산됩니다(위 일반 직원 산식과 다름).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 13 − 기산일의 월</t>
+          <t xml:space="preserve">     근속연수 = 당기 결산기준일의 연도 − 기산일의 연도</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     퇴직금 추계액 = [(급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) / 10] × 배수</t>
+          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 13 − 기산일의 월</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (평균급여 × 10% × 근속연수 × 배수 구조 — '10%'는 근속월 나머지항이 아니라 전체에 걸리는 계수입니다)</t>
+          <t xml:space="preserve">     퇴직금 추계액 = [(급여기준액 × 근속연수 + 급여기준액 × 근속월 / 10) / 10] × 배수</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
+          <t xml:space="preserve">     (평균급여 × 10% × 근속연수 × 배수 구조 — '10%'는 근속월 나머지항이 아니라 전체에 걸리는 계수입니다)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
+          <t xml:space="preserve">   '배수(임원)': 임원퇴직금지급규정 등에 따라 배수를 적용하는 회사만 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">     '부서' 값이 정확히 '임원'인 행에서만 이 값을 읽어 적용합니다(오탈자·다른 부서명이면 무시되고 일반 직원 산식으로 계산됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">     일반 직원 행은 이 칸에 값이 있어도 무시됩니다. 임원인데 배수를 비워두면 1배로 계산되고 비고에 안내가 남습니다.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr"/>
-    </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
-        </is>
-      </c>
+      <c r="A47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 명단의 '비고'에는 다음 두 가지가 자동으로 표시됩니다.</t>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 전기 결산기준일 기준 근속기간이 1년 미만이면 '전기 퇴직급여설정대상 아님(근속기간 1년 미만으로 추정)'</t>
+          <t xml:space="preserve">   퇴사자 명단의 '비고'에는 다음 두 가지가 자동으로 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       (근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건을 충족하지 못하므로, 이 인원은 애초에 전기말</t>
+          <t xml:space="preserve">     - 전기 결산기준일 기준 근속기간이 1년 미만이면 '전기 퇴직급여설정대상 아님(근속기간 1년 미만으로 추정)'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       퇴직급여충당부채 설정 대상이 아니었을 가능성이 있다는 안내입니다).</t>
+          <t xml:space="preserve">       (근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건을 충족하지 못하므로, 이 인원은 애초에 전기말</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">       퇴직급여충당부채 설정 대상이 아니었을 가능성이 있다는 안내입니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">     - '당기퇴사자' 시트(아래 5번)에 대응하는 지급액 입력이 없으면 '명단 비교 시 차이 있음' 경고.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr"/>
-    </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
-        </is>
-      </c>
+      <c r="A57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr"/>
-    </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
-        </is>
-      </c>
+      <c r="A64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr"/>
-    </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
-        </is>
-      </c>
+      <c r="A71" s="12" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr"/>
-    </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
-        </is>
-      </c>
+      <c r="A75" s="12" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1260,13 +1260,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1294,6 +1295,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>입사일(선택)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
@@ -1312,7 +1318,8 @@
       <c r="C3" s="5" t="n">
         <v>38500000</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>예시) 전기정보에 있는 사번으로 매칭 — 전기말 추계액과 자동 대사됨. 사번 없으면 성명으로 매칭.</t>
         </is>
@@ -1320,7 +1327,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1447,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A77"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1767,7 +1774,7 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">   퇴사자(자동 산출) = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
@@ -1781,164 +1788,220 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자 명단의 '비고'에는 다음 두 가지가 자동으로 표시됩니다.</t>
+          <t xml:space="preserve">   요약표의 '퇴사자 명단 대사' 표는 이 자동 산출 명단과 '당기퇴사자' 시트(아래 5번, 사용자 입력) 명단을</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 전기 결산기준일 기준 근속기간이 1년 미만이면 '전기 퇴직급여설정대상 아님(근속기간 1년 미만으로 추정)'</t>
+          <t xml:space="preserve">   나란히 놓고 비교합니다 — 양쪽에 모두 있으면 비고에 '이상없음', 한쪽에만 있으면 원인을 표시합니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       (근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건을 충족하지 못하므로, 이 인원은 애초에 전기말</t>
+          <t xml:space="preserve">     - 자동 산출 명단에만 있으면: '당기퇴사자 시트에 지급액 입력 없음'.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       퇴직급여충당부채 설정 대상이 아니었을 가능성이 있다는 안내입니다).</t>
+          <t xml:space="preserve">     - '당기퇴사자' 시트에만 있으면(전기정보 매칭 실패): 입력된 입사일(또는 전기정보 입사일) 기준</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - '당기퇴사자' 시트(아래 5번)에 대응하는 지급액 입력이 없으면 '명단 비교 시 차이 있음' 경고.</t>
+          <t xml:space="preserve">       전기 결산기준일 근속기간이 1년 미만이면 '전기 결산기준일 기준 근속 1년 미만 — 전기말</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr"/>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       퇴충설정대상 아님'(근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건 미충족), 그 외에는</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
+          <t xml:space="preserve">       '전기정보에서 매칭되는 인원을 찾지 못함(확인 필요)'.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+          <t xml:space="preserve">     - 양쪽에 다 있는데 그 인원이 '당기정보'에도 그대로 남아있으면(현재도 재직 중으로 보이면):</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
+          <t xml:space="preserve">       '당기정보에도 그대로 존재함 — 실제 퇴사 여부 확인 필요'.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+          <t xml:space="preserve">     - 같은 인원이 '당기퇴사자' 시트에 두 번 이상 입력되면 '이중기입의심' 경고(동명이인일 수도 있음).</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
-        </is>
-      </c>
+      <c r="A62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr"/>
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원(예: 근속 1년 미만이라 애초에 전기 인원현황에</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
+          <t xml:space="preserve">     없었던 경우)에 한해, 여기 입사일을 적어두면 전기 결산기준일 기준 근속 1년 미만 여부를 판단하는 데</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr"/>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     사용됩니다. 매칭이 되는 인원은 '전기정보'의 입사일을 그대로 쓰므로 비워둬도 됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
-        </is>
-      </c>
+      <c r="A72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr"/>
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -529,6 +530,11 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>대사용(선택)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
@@ -590,6 +596,11 @@
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>회사계상 퇴직금추계액(원)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -639,9 +650,12 @@
         <v>6000000</v>
       </c>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 실제 인원으로 교체(기존 재직자, 연간상여금 600만원 지급)</t>
+      <c r="L3" s="5" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 실제 인원으로 교체(기존 재직자, 연간상여금 600만원 지급). '회사계상 퇴직금추계액'을 채우면 앱 계산값과 자동 대사(차이 유의적이면 강조)</t>
         </is>
       </c>
     </row>
@@ -689,9 +703,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 기존 재직자(상여금 없음)</t>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 기존 재직자(상여금 없음, 회사계상액 모름 — 비워두면 대사만 생략)</t>
         </is>
       </c>
     </row>
@@ -739,7 +754,8 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>예시) 당기 중 신규입사 — '전기정보'에는 없어 요약표의 '신규입사자 명단'에 자동 표시됨</t>
         </is>
@@ -793,7 +809,8 @@
         <v>4200000</v>
       </c>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>예시) 퇴직금 중간정산 이력 있음 — 재직 상태는 계속 유지되며(퇴사 아님), 재직일수만 입사일(2018-06-01)이 아닌 중간정산일(2023-06-30)부터 다시 기산됨</t>
         </is>
@@ -845,18 +862,20 @@
       <c r="K7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>예시) 임원퇴직금지급규정상 배수 2배 적용 — 부서명이 정확히 '임원'인 인원에만 배수가 적용됨</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="L1"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="M1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="L1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F3:F300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="제조원가 또는 판관비 중 선택하세요." type="list">
@@ -873,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -887,7 +906,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -916,6 +936,11 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>대사용(선택)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
@@ -977,6 +1002,11 @@
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>회사계상 퇴직금추계액(원)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1026,9 +1056,12 @@
         <v>5500000</v>
       </c>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 당기와 동일 인원(전기 시점 급여). 이 시트의 급여는 계산에 쓰이지 않음(매칭용)</t>
+      <c r="L3" s="5" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>예시 행 — 당기와 동일 인원(전기 시점 급여). 이 시트의 급여는 계산에 쓰이지 않음(매칭용). '회사계상 퇴직금추계액'만 전기말 대사에 쓰임</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1109,8 @@
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 당기와 동일 인원</t>
         </is>
@@ -1130,7 +1164,8 @@
         <v>4200000</v>
       </c>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 당기와 동일 인원(중간정산 이력 포함)</t>
         </is>
@@ -1182,7 +1217,8 @@
       <c r="K6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>예시 행 — 당기와 동일 인원</t>
         </is>
@@ -1232,18 +1268,20 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>예시) 당기 중 퇴사 — '당기정보'에는 이 사번이 없어 요약표의 '퇴사자 명단'에 자동 표시됨</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="L1"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="M1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="L1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F3:F300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="제조원가 또는 판관비 중 선택하세요." type="list">
@@ -1454,7 +1492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1755,253 +1793,295 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr"/>
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '회사계상 퇴직금추계액(원)' (선택): 감가상각비 앱의 '당기 회사계상 감가상각비'와 같은 용도입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
+          <t xml:space="preserve">     회사가 인원별로 이미 계산해둔 퇴직금 추계액(퇴직연금 명세, 인사시스템 등)을 알면 채워 넣으세요.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">     '당기정보'에 채우면 당기말 계산값과, '전기정보'에 채우면 전기말 계산값과 인별로 자동 대사되어</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   퇴사자(자동 산출) = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
+          <t xml:space="preserve">     '인원별추계명세'/'전기인원별추계명세' 시트에 차이가 표시되고 유의차이는 노란색으로 강조됩니다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
+          <t xml:space="preserve">     원가구분별 총액 차이가 어디서 나는지(어느 개인 때문인지) 찾을 때 특히 유용합니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   요약표의 '퇴사자 명단 대사' 표는 이 자동 산출 명단과 '당기퇴사자' 시트(아래 5번, 사용자 입력) 명단을</t>
+          <t xml:space="preserve">     모르면 비워둬도 앱 실행에는 문제 없습니다(해당 인원만 대사가 생략됨).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   나란히 놓고 비교합니다 — 양쪽에 모두 있으면 비고에 '이상없음', 한쪽에만 있으면 원인을 표시합니다.</t>
-        </is>
-      </c>
+      <c r="A53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 자동 산출 명단에만 있으면: '당기퇴사자 시트에 지급액 입력 없음'.</t>
+          <t>4. 신규입사자/퇴사자 명단 (요약표에 자동 산출)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - '당기퇴사자' 시트에만 있으면(전기정보 매칭 실패): 입력된 입사일(또는 전기정보 입사일) 기준</t>
+          <t xml:space="preserve">   신규입사자 = '당기정보'에는 있으나 '전기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       전기 결산기준일 근속기간이 1년 미만이면 '전기 결산기준일 기준 근속 1년 미만 — 전기말</t>
+          <t xml:space="preserve">   퇴사자(자동 산출) = '전기정보'에는 있으나 '당기정보'에는 없는 사번(또는 성명).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       퇴충설정대상 아님'(근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건 미충족), 그 외에는</t>
+          <t xml:space="preserve">   '전기정보' 시트를 비워두면(또는 시트 자체를 지우면) 인원변동 명단만 생략되고 당기 계산은 정상 진행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       '전기정보에서 매칭되는 인원을 찾지 못함(확인 필요)'.</t>
+          <t xml:space="preserve">   요약표의 '퇴사자 명단 대사' 표는 이 자동 산출 명단과 '당기퇴사자' 시트(아래 5번, 사용자 입력) 명단을</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 양쪽에 다 있는데 그 인원이 '당기정보'에도 그대로 남아있으면(현재도 재직 중으로 보이면):</t>
+          <t xml:space="preserve">   나란히 놓고 비교합니다 — 양쪽에 모두 있으면 비고에 '이상없음', 한쪽에만 있으면 원인을 표시합니다.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       '당기정보에도 그대로 존재함 — 실제 퇴사 여부 확인 필요'.</t>
+          <t xml:space="preserve">     - 자동 산출 명단에만 있으면: '당기퇴사자 시트에 지급액 입력 없음'.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 같은 인원이 '당기퇴사자' 시트에 두 번 이상 입력되면 '이중기입의심' 경고(동명이인일 수도 있음).</t>
+          <t xml:space="preserve">     - '당기퇴사자' 시트에만 있으면(전기정보 매칭 실패): 입력된 입사일(또는 전기정보 입사일) 기준</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr"/>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       전기 결산기준일 근속기간이 1년 미만이면 '전기 결산기준일 기준 근속 1년 미만 — 전기말</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
+          <t xml:space="preserve">       퇴충설정대상 아님'(근로기준법상 계속근로기간 1년 미만은 퇴직금 지급 요건 미충족), 그 외에는</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
+          <t xml:space="preserve">       '전기정보에서 매칭되는 인원을 찾지 못함(확인 필요)'.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
+          <t xml:space="preserve">     - 양쪽에 다 있는데 그 인원이 '당기정보'에도 그대로 남아있으면(현재도 재직 중으로 보이면):</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+          <t xml:space="preserve">       '당기정보에도 그대로 존재함 — 실제 퇴사 여부 확인 필요'.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+          <t xml:space="preserve">     - 같은 인원이 '당기퇴사자' 시트에 두 번 이상 입력되면 '이중기입의심' 경고(동명이인일 수도 있음).</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
-        </is>
-      </c>
+      <c r="A68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원(예: 근속 1년 미만이라 애초에 전기 인원현황에</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     없었던 경우)에 한해, 여기 입사일을 적어두면 전기 결산기준일 기준 근속 1년 미만 여부를 판단하는 데</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     사용됩니다. 매칭이 되는 인원은 '전기정보'의 입사일을 그대로 쓰므로 비워둬도 됩니다.</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr"/>
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원(예: 근속 1년 미만이라 애초에 전기 인원현황에</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+          <t xml:space="preserve">     없었던 경우)에 한해, 여기 입사일을 적어두면 전기 결산기준일 기준 근속 1년 미만 여부를 판단하는 데</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+          <t xml:space="preserve">     사용됩니다. 매칭이 되는 인원은 '전기정보'의 입사일을 그대로 쓰므로 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
-        </is>
-      </c>
+      <c r="A78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr"/>
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="inlineStr"/>
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
           <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1753,7 +1753,7 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 13 − 기산일의 월</t>
+          <t xml:space="preserve">     근속월(1년 미만 잔여월 보정) = 12 − 기산일의 월</t>
         </is>
       </c>
     </row>

--- a/severance_analyzer/input_data/severance_template.xlsx
+++ b/severance_analyzer/input_data/severance_template.xlsx
@@ -1298,14 +1298,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1333,10 +1334,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>지급사유(실제퇴사/중간정산)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>입사일(선택)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1356,17 +1362,53 @@
       <c r="C3" s="5" t="n">
         <v>38500000</v>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>실제퇴사</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>예시) 전기정보에 있는 사번으로 매칭 — 전기말 추계액과 자동 대사됨. 사번 없으면 성명으로 매칭.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EMP-1004</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>예시)박민수</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>중간정산</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>예시) 재직 중 퇴직금 중간정산 — '당기정보'에 그대로 남아있는 게 정상이며, 요약표 '퇴사자 명단 대사' 표의 비고에 '중간정산'으로만 표시되고 '당기정보에도 존재함' 경고는 뜨지 않음</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D3:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="실제퇴사 또는 중간정산 중 선택하세요." type="list">
+      <formula1>"실제퇴사,중간정산"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1492,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:A97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1924,164 +1966,206 @@
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       '당기정보에도 그대로 존재함 — 실제 퇴사 여부 확인 필요'.</t>
+          <t xml:space="preserve">       '당기정보에도 그대로 존재함 — 실제 퇴사 여부 확인 필요'. 단, '당기퇴사자' 시트의 지급사유가</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - 같은 인원이 '당기퇴사자' 시트에 두 번 이상 입력되면 '이중기입의심' 경고(동명이인일 수도 있음).</t>
+          <t xml:space="preserve">       '중간정산'이면 이 경고 대신 그냥 '중간정산'으로 표시됩니다(재직 중 중간정산은 당기정보에</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr"/>
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       그대로 남아있는 게 정상이므로).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>5. '당기퇴사자' 시트 (선택) — 퇴사자의 실제 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
+          <t xml:space="preserve">     - 같은 인원이 '당기퇴사자' 시트에 두 번 이상 입력되면 '이중기입의심' 경고(동명이인일 수도 있음).</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
-        </is>
-      </c>
+      <c r="A70" s="12" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
+          <t>5. '당기퇴사자' 시트 (선택) — 퇴직금(퇴직연금) 지급액을 알면 채워서 인별 대사를 추가로 받을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
+          <t xml:space="preserve">   '사번'(없으면 성명) + '실제지급액(원)'만 입력하면, 앱이 '전기정보' 시트에서 같은 사번(성명)을 찾아</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
+          <t xml:space="preserve">   그 사람의 전기말 추계액과 자동으로 비교(대사)해 요약표에 표시합니다. 사업장/부서/직급 등은</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
+          <t xml:space="preserve">   '전기정보'에서 그대로 가져오므로 다시 입력할 필요가 없습니다. 모르는 퇴사자는 행을 비워두면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원(예: 근속 1년 미만이라 애초에 전기 인원현황에</t>
+          <t xml:space="preserve">   (해당 인원만 대사가 생략되고, 나머지 재계산·집계에는 영향이 없습니다).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     없었던 경우)에 한해, 여기 입사일을 적어두면 전기 결산기준일 기준 근속 1년 미만 여부를 판단하는 데</t>
+          <t xml:space="preserve">   '지급사유(실제퇴사/중간정산)': 대한민국 퇴직금 지급 사유는 크게 '실제퇴사'와 '중간정산'(재직 중</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     사용됩니다. 매칭이 되는 인원은 '전기정보'의 입사일을 그대로 쓰므로 비워둬도 됩니다.</t>
+          <t xml:space="preserve">     퇴직금을 미리 정산받는 것) 두 가지입니다. 반드시 구분해서 선택하세요 — '중간정산'으로 표시하면</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="inlineStr"/>
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     앱이 이 인원을 진짜 퇴사자로 취급하지 않고, '당기정보'에 그대로 남아있어도 경고를 띄우지 않습니다</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+          <t xml:space="preserve">     (비워두면 '실제퇴사'로 간주해 기존처럼 처리됩니다).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
+          <t xml:space="preserve">   같은 인원(사번/성명)이 두 번 이상 입력되면 '이중기입의심' 경고가 표시됩니다(동명이인일 수도 있으니 확인).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
+          <t xml:space="preserve">   '입사일(선택)': '전기정보'에서 매칭이 안 되는 인원(예: 근속 1년 미만이라 애초에 전기 인원현황에</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
+          <t xml:space="preserve">     없었던 경우)에 한해, 여기 입사일을 적어두면 전기 결산기준일 기준 근속 1년 미만 여부를 판단하는 데</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+          <t xml:space="preserve">     사용됩니다. 매칭이 되는 인원은 '전기정보'의 입사일을 그대로 쓰므로 비워둬도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
-        </is>
-      </c>
+      <c r="A84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr"/>
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>6. '기준정보' 시트 — 전기말/당기말 회사계상 퇴직급여충당부채(제조원가분/판관비분) 4칸과,</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+          <t xml:space="preserve">   당기 퇴직급여충당부채 차변(당기지급액) 1칸을 입력합니다. 다섯 값 모두 인별 재계산액과의 대사(비교)용</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+          <t xml:space="preserve">   참고값일 뿐, 재계산 자체(전기말·당기말·당기 퇴직급여)에는 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+          <t xml:space="preserve">   '당기지급액'은 journal_analyzer(분개장분석) 메뉴에서 '퇴직급여충당부채' 계정의 당기 차변 합계를</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="inlineStr"/>
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   뽑아 입력하면 됩니다 — 전기말(회사계상)+당기 퇴직급여(재계산)-당기지급액이 당기말(회사계상)과</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   맞는지 요약표에서 자동으로 T계정 검증(tie-out)합니다. 모르면 비워둬도 됩니다(해당 검증만 생략).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>7. 결산기준일은 이 파일에 입력하지 않습니다. 실행 시 파일명의 'fy&lt;연도&gt;'와 --fiscal-month 옵션(기본 12월)으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   depreciation_analyzer/lease_analyzer와 동일한 규칙으로 당기말·전기말 결산기준일을 자동 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   예) --fiscal-month 12 --fiscal-year 2026 → 당기말 2026-12-31, 전기말 2025-12-31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
           <t>8. 파일명 규칙: 이 템플릿을 복사해 'severance_&lt;회사명&gt;_information_fy&lt;회계연도&gt;.xlsx' 로 저장하세요.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   예) severance_kyungnam_information_fy2026.xlsx (전기·당기 데이터가 모두 이 한 파일 안에 들어갑니다).</t>
         </is>
